--- a/Docs/Test_Suite.xlsx
+++ b/Docs/Test_Suite.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Разні курси\Testing QA\для гіту і нотіону\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD5006D-0CE3-4F79-9755-444A385AE199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135E8432-4DCA-474C-BD30-790E52D91DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="911" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -221,9 +221,6 @@
     <t>Відкривається сторінка корзини, товари відображаються коректно</t>
   </si>
   <si>
-    <t>Натиснути "Check Out" в корзині</t>
-  </si>
-  <si>
     <t>Відкривається сторінка оформлення замовлення</t>
   </si>
   <si>
@@ -338,9 +335,6 @@
     <t>Перевірка поведінки кошика при критичному піку (Stress Test)</t>
   </si>
   <si>
-    <t>Поступово збільшувати кількість запитів до кошика, поки сервер не перестане відповідати</t>
-  </si>
-  <si>
     <t>Система коректно обробляє чергу, а при падінні повертає зрозумілу сторінку помилки (напр. 503 Service Unavailable).</t>
   </si>
   <si>
@@ -358,9 +352,6 @@
   <si>
     <t>1. Натиснути "Check Out" на сторінці товару
 2. Натиснути "х" на сторінці корзини, біля того товару який треба видалити</t>
-  </si>
-  <si>
-    <t>Товар видаляється з корзини, лічильник кількості товарів оновляються</t>
   </si>
   <si>
     <t>Видалення вмісту корзини через POST-запит</t>
@@ -426,9 +417,6 @@
   </si>
   <si>
     <t>Успішний перехід на сторінку корзини</t>
-  </si>
-  <si>
-    <t>Натиснути на кнопку "х" напроти товару</t>
   </si>
   <si>
     <t>Товар видалено видалено. Корзина пуста</t>
@@ -464,9 +452,6 @@
     <t>Змінити кількість товару в випадаючій корзині ввівши літеру</t>
   </si>
   <si>
-    <t>Ввести лутеру в поле кількості товару в випадаючій корзині</t>
-  </si>
-  <si>
     <t>Відображається повідомлення про помилку введення</t>
   </si>
   <si>
@@ -517,9 +502,6 @@
   </si>
   <si>
     <t>Відправити POST запит на /cart/add.js з невалідним id</t>
-  </si>
-  <si>
-    <t>Відправити POST запит на /cart/add.js з валідним id та quantity</t>
   </si>
   <si>
     <t>Натиснути кнопку "Send"</t>
@@ -859,9 +841,6 @@
   </si>
   <si>
     <t>Натиснути на кнопку "Add to cart" декілька разів</t>
-  </si>
-  <si>
-    <t>5+ кліків</t>
   </si>
   <si>
     <t>Кнопка стає неактивною після першого кліку</t>
@@ -1057,9 +1036,6 @@
     <t>Thread Group налаштовано</t>
   </si>
   <si>
-    <t>HTTP Request налаштовано</t>
-  </si>
-  <si>
     <t>Запуск тестування</t>
   </si>
   <si>
@@ -1325,9 +1301,6 @@
     <t>Після додавання товару до корзини, товар відображається у випадаючій корзині</t>
   </si>
   <si>
-    <t>Після додавання товару до корзини, відбувається вічна загрузка у випадаючіц корзині</t>
-  </si>
-  <si>
     <t>Environment</t>
   </si>
   <si>
@@ -1338,9 +1311,6 @@
   </si>
   <si>
     <t xml:space="preserve">При відкриті випадаючої корзини відразу після додавання будь-якого товару, товар додається до корзини, але у випадаючій корзині відбувається вічна загрузка. </t>
-  </si>
-  <si>
-    <t>Якщо після додавання товару до корзини, обновити сторінку, то товар буде відображатись у випадаючій корзині</t>
   </si>
   <si>
     <t>Frequency</t>
@@ -1413,9 +1383,6 @@
       </rPr>
       <t xml:space="preserve"> https://surl.li/wzjmhz</t>
     </r>
-  </si>
-  <si>
-    <t>Тест успішно пройдено після виправлення конфігурації CSV-файлу</t>
   </si>
   <si>
     <r>
@@ -1521,12 +1488,6 @@
 Виявлено обмеження швидкості запитів (HTTP 429 Too Many Requests). Сервер швидко обробляє запити (90-147 мс), проте вмикається механізм захисту від DDoS або інтенсивного трафіку, що призводить до відхилення 40% запитів при навантаженні 10 користувачів.</t>
   </si>
   <si>
-    <t>Змінна кількості товару на велике число приводить сайт до помилки</t>
-  </si>
-  <si>
-    <t>При змінні кількості товару на 99999999, сайт видає помилку "Something went wrong."</t>
-  </si>
-  <si>
     <t>1. Перейти на сторінку товару(https://sauce-demo.myshopify.com/collections/frontpage/products/grey-jacket)
 2. Натиснути кнопку "Add to Cart"
 3. Обновити сторінку.
@@ -1645,22 +1606,10 @@
     <t>Елемент має бути прихований</t>
   </si>
   <si>
-    <t>Надпис "Footer" відображається на сторінці сайту</t>
-  </si>
-  <si>
     <t>Не видалений рядок коду  &lt;h2&gt;Footer&lt;/h2&gt;</t>
   </si>
   <si>
-    <t>1. Проскролити сайт до футеру
-2. Звернути увагу на надпис "Footer"</t>
-  </si>
-  <si>
     <t>На сторінці сайту відображається технічний текст "Footer"</t>
-  </si>
-  <si>
-    <t>OS: Windows 10
-Browser: Google Chrome 149.0.7827.103, Opera GX 132.0.5905.43
-Resolution: 1920x1200</t>
   </si>
   <si>
     <r>
@@ -1683,6 +1632,120 @@
         <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> https://surl.li/cbcwmd</t>
+    </r>
+  </si>
+  <si>
+    <t>Товар видаляється з корзини, лічильник кількості товарів оновлюються</t>
+  </si>
+  <si>
+    <t>Натиснути "Check Out" на сторінці корзини</t>
+  </si>
+  <si>
+    <t>Відправити POST запит на /cart/add.js з валідними id та quantity для двох товарів</t>
+  </si>
+  <si>
+    <t>Емулювати одночасне додавання товарів у кошик 2000 користувачами за 30 секунд</t>
+  </si>
+  <si>
+    <t>Натиснути на кнопку "х" навпроти товару</t>
+  </si>
+  <si>
+    <t>Ввести літеру в поле кількості товару в випадаючій корзині</t>
+  </si>
+  <si>
+    <t>Налаштування HTTP Request починається</t>
+  </si>
+  <si>
+    <t>Bug_03 
+Тест успішно пройдено після виправлення конфігурації CSV-файлу</t>
+  </si>
+  <si>
+    <t>Після додавання товару до корзини, відбувається вічна загрузка у випадаючій корзині</t>
+  </si>
+  <si>
+    <t>Якщо після додавання товару до корзини, оновити сторінку, то товар буде відображатись у випадаючій корзині</t>
+  </si>
+  <si>
+    <t>Зміна кількості товару на велике число призводить сайт до помилки</t>
+  </si>
+  <si>
+    <t>При зміні кількості товару на 99999999, сайт видає помилку "Something went wrong."</t>
+  </si>
+  <si>
+    <t>1. Проскролити сайт до футеру
+2. Звернути увагу на напис "Footer"</t>
+  </si>
+  <si>
+    <t>Напис "Footer" відображається на сторінці сайту</t>
+  </si>
+  <si>
+    <t>10 кліків</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">OS: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">Windows 10
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Browser:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> Google Chrome 149.0.7827.103, Opera GX 132.0.5905.43
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Resolution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> 1920x1200</t>
     </r>
   </si>
 </sst>
@@ -1801,7 +1864,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1812,13 +1875,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1828,9 +1885,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1867,9 +1921,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1887,9 +1938,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1910,6 +1958,18 @@
     </xf>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2294,13 +2354,13 @@
   <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="47.109375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="22" style="5" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="34.77734375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="34.109375" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="5"/>
+    <col min="1" max="1" width="10.77734375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="47.109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="22" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="34.77734375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="34.109375" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -2313,14 +2373,14 @@
       <c r="C1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.3">
@@ -2333,7 +2393,7 @@
       <c r="C2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -2347,20 +2407,20 @@
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="34" t="s">
         <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>97</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="90" x14ac:dyDescent="0.3">
@@ -2373,14 +2433,14 @@
       <c r="C4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>96</v>
+      <c r="E4" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>97</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.3">
@@ -2393,13 +2453,13 @@
       <c r="C5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="2" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2413,13 +2473,13 @@
       <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="2" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2427,19 +2487,19 @@
       <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="2" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2453,7 +2513,7 @@
       <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -2473,7 +2533,7 @@
       <c r="C9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -2493,7 +2553,7 @@
       <c r="C10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -2513,10 +2573,10 @@
       <c r="C11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="2" t="s">
         <v>53</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -2533,10 +2593,10 @@
       <c r="C12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="2" t="s">
         <v>53</v>
       </c>
       <c r="F12" s="2" t="s">
@@ -2548,19 +2608,19 @@
         <v>29</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="108" x14ac:dyDescent="0.3">
@@ -2573,14 +2633,14 @@
       <c r="C14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>63</v>
+      <c r="E14" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="108" x14ac:dyDescent="0.3">
@@ -2593,14 +2653,14 @@
       <c r="C15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>64</v>
+      <c r="E15" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="108" x14ac:dyDescent="0.3">
@@ -2608,19 +2668,19 @@
         <v>32</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>65</v>
+      <c r="E16" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="108" x14ac:dyDescent="0.3">
@@ -2633,14 +2693,14 @@
       <c r="C17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>66</v>
+      <c r="E17" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="108" x14ac:dyDescent="0.3">
@@ -2653,19 +2713,19 @@
       <c r="C18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>67</v>
+      <c r="E18" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="108" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>27</v>
@@ -2673,19 +2733,19 @@
       <c r="C19" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>68</v>
+      <c r="E19" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>34</v>
@@ -2696,231 +2756,231 @@
       <c r="D20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>58</v>
+      <c r="E20" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>143</v>
+      <c r="E21" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>92</v>
+      <c r="E22" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="90" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>144</v>
+      <c r="E23" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>145</v>
+      <c r="E24" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>146</v>
+      <c r="E25" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>80</v>
+        <v>163</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>79</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>147</v>
+      <c r="E26" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>145</v>
+      <c r="E27" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>93</v>
+      <c r="E28" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="90" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>86</v>
+      <c r="E29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>88</v>
+      <c r="E30" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="90" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>90</v>
+        <v>339</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2936,197 +2996,197 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="9"/>
-    <col min="2" max="2" width="40" style="9" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="40" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
+      <c r="A1" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
     </row>
     <row r="2" spans="1:5" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
+      <c r="A2" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>104</v>
+      <c r="D3" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" s="18"/>
+      <c r="B4" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" s="15"/>
     </row>
     <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>148</v>
+      <c r="B5" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="E5" s="18"/>
+      <c r="D5" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:5" ht="158.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>179</v>
+      <c r="E6" s="23" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="72" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="26" t="s">
-        <v>155</v>
+      <c r="B7" s="22" t="s">
+        <v>149</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>181</v>
+      <c r="D7" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="22"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="22"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="22"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="22"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="22"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="22"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="22"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="22"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="22"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3146,197 +3206,197 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="9"/>
-    <col min="2" max="2" width="40" style="9" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="40" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
+      <c r="A1" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
     </row>
     <row r="2" spans="1:5" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="40" t="s">
-        <v>184</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
+      <c r="A2" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>104</v>
+      <c r="D3" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" s="18"/>
+      <c r="B4" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" s="15"/>
     </row>
     <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>148</v>
+      <c r="B5" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="E5" s="18"/>
+      <c r="D5" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:5" ht="158.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>185</v>
+      <c r="E6" s="23" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="108" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="26" t="s">
-        <v>155</v>
+      <c r="B7" s="22" t="s">
+        <v>149</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="E7" s="18" t="s">
-        <v>186</v>
-      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="22"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="22"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="22"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="22"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="22"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="22"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="22"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="22"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="22"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3356,241 +3416,241 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="9"/>
-    <col min="2" max="2" width="40" style="9" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="40" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
+      <c r="A1" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
     </row>
     <row r="2" spans="1:5" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
+      <c r="A2" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>104</v>
+      <c r="D3" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" s="18"/>
+      <c r="B4" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" s="15"/>
     </row>
     <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="18" t="s">
-        <v>138</v>
+      <c r="B5" s="15" t="s">
+        <v>133</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" s="18"/>
+      <c r="D5" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:5" ht="54" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>3</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>139</v>
+      <c r="B6" s="15" t="s">
+        <v>134</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="E6" s="18"/>
+      <c r="D6" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="E6" s="15"/>
     </row>
     <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>194</v>
+      <c r="B7" s="15" t="s">
+        <v>188</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="E7" s="18"/>
+        <v>184</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="15"/>
     </row>
     <row r="8" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>5</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>195</v>
+      <c r="B8" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
       </c>
-      <c r="D8" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E8" s="18"/>
+      <c r="D8" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" s="15"/>
     </row>
     <row r="9" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>6</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>140</v>
+      <c r="B9" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="E9" s="18"/>
+        <v>136</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="E9" s="15"/>
     </row>
     <row r="10" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>7</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>153</v>
+      <c r="B10" s="15" t="s">
+        <v>147</v>
       </c>
       <c r="C10" s="3">
         <v>0</v>
       </c>
-      <c r="D10" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="E10" s="18"/>
+      <c r="D10" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" s="15"/>
     </row>
     <row r="11" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>8</v>
       </c>
-      <c r="B11" s="26" t="s">
-        <v>148</v>
+      <c r="B11" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="18"/>
+      <c r="D11" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E11" s="15"/>
     </row>
     <row r="12" spans="1:5" ht="116.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>192</v>
+      <c r="E12" s="23" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="90" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>10</v>
       </c>
-      <c r="B13" s="26" t="s">
-        <v>155</v>
+      <c r="B13" s="22" t="s">
+        <v>149</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>193</v>
+      <c r="D13" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="22"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="22"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="22"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3610,241 +3670,241 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="9"/>
-    <col min="2" max="2" width="40" style="9" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="40" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
-        <v>211</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
+      <c r="A1" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
     </row>
     <row r="2" spans="1:5" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="A2" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="30" t="s">
-        <v>104</v>
+      <c r="D3" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" s="29"/>
+      <c r="B4" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" s="25"/>
     </row>
     <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="29" t="s">
-        <v>138</v>
+      <c r="B5" s="25" t="s">
+        <v>133</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" s="29"/>
+      <c r="D5" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E5" s="25"/>
     </row>
     <row r="6" spans="1:5" ht="54" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>3</v>
       </c>
-      <c r="B6" s="29" t="s">
-        <v>139</v>
+      <c r="B6" s="25" t="s">
+        <v>134</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="E6" s="29"/>
+      <c r="D6" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="E6" s="25"/>
     </row>
     <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>151</v>
+      <c r="B7" s="25" t="s">
+        <v>145</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="E7" s="29"/>
+        <v>137</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="25"/>
     </row>
     <row r="8" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>5</v>
       </c>
-      <c r="B8" s="29" t="s">
-        <v>152</v>
+      <c r="B8" s="25" t="s">
+        <v>146</v>
       </c>
       <c r="C8" s="3">
         <v>99999</v>
       </c>
-      <c r="D8" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="E8" s="29"/>
+      <c r="D8" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" s="25"/>
     </row>
     <row r="9" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>6</v>
       </c>
-      <c r="B9" s="29" t="s">
-        <v>140</v>
+      <c r="B9" s="25" t="s">
+        <v>135</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="E9" s="29"/>
+        <v>136</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="E9" s="25"/>
     </row>
     <row r="10" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>7</v>
       </c>
-      <c r="B10" s="29" t="s">
-        <v>153</v>
+      <c r="B10" s="25" t="s">
+        <v>147</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
       </c>
-      <c r="D10" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="E10" s="29"/>
+      <c r="D10" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" s="25"/>
     </row>
     <row r="11" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>8</v>
       </c>
-      <c r="B11" s="26" t="s">
-        <v>148</v>
+      <c r="B11" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="29"/>
+      <c r="D11" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="E11" s="25"/>
     </row>
     <row r="12" spans="1:5" ht="144" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="E12" s="29" t="s">
-        <v>213</v>
+      <c r="E12" s="25" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="108" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>10</v>
       </c>
-      <c r="B13" s="26" t="s">
-        <v>155</v>
+      <c r="B13" s="22" t="s">
+        <v>149</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="29" t="s">
-        <v>212</v>
-      </c>
-      <c r="E13" s="29" t="s">
-        <v>214</v>
+      <c r="D13" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="22"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="22"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="22"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3864,273 +3924,273 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="9"/>
-    <col min="2" max="2" width="40" style="9" customWidth="1"/>
-    <col min="3" max="3" width="20.44140625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="40" style="7" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
-        <v>182</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
+      <c r="A1" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
     </row>
     <row r="2" spans="1:5" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="A2" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>104</v>
+      <c r="D3" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" s="29"/>
+      <c r="B4" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" s="25"/>
     </row>
     <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="29" t="s">
-        <v>138</v>
+      <c r="B5" s="25" t="s">
+        <v>133</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" s="29"/>
+      <c r="D5" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E5" s="25"/>
     </row>
     <row r="6" spans="1:5" ht="54" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>3</v>
       </c>
-      <c r="B6" s="29" t="s">
-        <v>139</v>
+      <c r="B6" s="25" t="s">
+        <v>134</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="E6" s="29"/>
+      <c r="D6" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="E6" s="25"/>
     </row>
     <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>151</v>
+      <c r="B7" s="25" t="s">
+        <v>145</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="E7" s="29"/>
+        <v>197</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="25"/>
     </row>
     <row r="8" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>5</v>
       </c>
-      <c r="B8" s="29" t="s">
-        <v>152</v>
+      <c r="B8" s="25" t="s">
+        <v>146</v>
       </c>
       <c r="C8" s="3">
         <v>611945025</v>
       </c>
-      <c r="D8" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="E8" s="29"/>
+      <c r="D8" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" s="25"/>
     </row>
     <row r="9" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>6</v>
       </c>
-      <c r="B9" s="29" t="s">
-        <v>140</v>
+      <c r="B9" s="25" t="s">
+        <v>135</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="E9" s="29"/>
+        <v>198</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="E9" s="25"/>
     </row>
     <row r="10" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>7</v>
       </c>
-      <c r="B10" s="29" t="s">
-        <v>153</v>
+      <c r="B10" s="25" t="s">
+        <v>147</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
       </c>
-      <c r="D10" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="E10" s="29"/>
+      <c r="D10" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" s="25"/>
     </row>
     <row r="11" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>8</v>
       </c>
-      <c r="B11" s="29" t="s">
-        <v>151</v>
+      <c r="B11" s="25" t="s">
+        <v>145</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="E11" s="29"/>
+        <v>199</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="E11" s="25"/>
     </row>
     <row r="12" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="29" t="s">
-        <v>152</v>
+      <c r="B12" s="25" t="s">
+        <v>146</v>
       </c>
       <c r="C12" s="3">
         <v>611952521</v>
       </c>
-      <c r="D12" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="E12" s="29"/>
+      <c r="D12" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="E12" s="25"/>
     </row>
     <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>10</v>
       </c>
-      <c r="B13" s="29" t="s">
-        <v>140</v>
+      <c r="B13" s="25" t="s">
+        <v>135</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="E13" s="29"/>
+        <v>200</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="E13" s="25"/>
     </row>
     <row r="14" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>11</v>
       </c>
-      <c r="B14" s="29" t="s">
-        <v>153</v>
+      <c r="B14" s="25" t="s">
+        <v>147</v>
       </c>
       <c r="C14" s="3">
         <v>2</v>
       </c>
-      <c r="D14" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="E14" s="29"/>
+      <c r="D14" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14" s="25"/>
     </row>
     <row r="15" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>12</v>
       </c>
-      <c r="B15" s="26" t="s">
-        <v>148</v>
+      <c r="B15" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="E15" s="29"/>
+      <c r="D15" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" s="25"/>
     </row>
     <row r="16" spans="1:5" ht="129" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>209</v>
+      <c r="E16" s="23" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="144" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>14</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>155</v>
+      <c r="B17" s="22" t="s">
+        <v>149</v>
       </c>
       <c r="C17" s="3"/>
-      <c r="D17" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>210</v>
+      <c r="D17" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4150,281 +4210,281 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="9"/>
-    <col min="2" max="2" width="40" style="9" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="40" style="7" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
-        <v>229</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
+      <c r="A1" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
     </row>
     <row r="2" spans="1:5" ht="150" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="43" t="s">
-        <v>228</v>
-      </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="A2" s="42" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="30" t="s">
-        <v>104</v>
+      <c r="D3" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="54" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>222</v>
-      </c>
-      <c r="E4" s="29"/>
+      <c r="B4" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="E4" s="25"/>
     </row>
     <row r="5" spans="1:5" ht="54" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="29" t="s">
-        <v>230</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>259</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>231</v>
-      </c>
-      <c r="E5" s="29"/>
+      <c r="B5" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="E5" s="25"/>
     </row>
     <row r="6" spans="1:5" ht="72" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>3</v>
       </c>
-      <c r="B6" s="29" t="s">
-        <v>232</v>
+      <c r="B6" s="25" t="s">
+        <v>224</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>238</v>
-      </c>
-      <c r="E6" s="29"/>
+        <v>225</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="E6" s="25"/>
     </row>
     <row r="7" spans="1:5" ht="54" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>234</v>
+      <c r="B7" s="25" t="s">
+        <v>226</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>239</v>
-      </c>
-      <c r="E7" s="29"/>
+        <v>227</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="E7" s="25"/>
     </row>
     <row r="8" spans="1:5" ht="90" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>5</v>
       </c>
-      <c r="B8" s="29" t="s">
-        <v>236</v>
+      <c r="B8" s="25" t="s">
+        <v>228</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="E8" s="29"/>
+        <v>229</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="E8" s="25"/>
     </row>
     <row r="9" spans="1:5" ht="90" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>226</v>
+        <v>219</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="90" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>7</v>
       </c>
-      <c r="B10" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="E10" s="29"/>
+      <c r="B10" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>342</v>
+      </c>
+      <c r="E10" s="25"/>
     </row>
     <row r="11" spans="1:5" ht="54" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>8</v>
       </c>
-      <c r="B11" s="29" t="s">
-        <v>242</v>
+      <c r="B11" s="25" t="s">
+        <v>234</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>244</v>
-      </c>
-      <c r="E11" s="29"/>
+        <v>235</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="E11" s="25"/>
     </row>
     <row r="12" spans="1:5" ht="54" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="29" t="s">
-        <v>245</v>
+      <c r="B12" s="25" t="s">
+        <v>237</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="E12" s="29"/>
+        <v>238</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="E12" s="25"/>
     </row>
     <row r="13" spans="1:5" ht="54" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>251</v>
+        <v>241</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>243</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E13" s="32"/>
+        <v>240</v>
+      </c>
+      <c r="E13" s="27"/>
     </row>
     <row r="14" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>11</v>
       </c>
-      <c r="B14" s="29" t="s">
-        <v>253</v>
+      <c r="B14" s="25" t="s">
+        <v>245</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="E14" s="29"/>
+      <c r="D14" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="E14" s="25"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>12</v>
       </c>
-      <c r="B15" s="29" t="s">
-        <v>220</v>
+      <c r="B15" s="25" t="s">
+        <v>213</v>
       </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="E15" s="29"/>
+      <c r="D15" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="E15" s="25"/>
     </row>
     <row r="16" spans="1:5" ht="198" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>13</v>
       </c>
-      <c r="B16" s="29" t="s">
-        <v>221</v>
+      <c r="B16" s="25" t="s">
+        <v>214</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="E16" s="29"/>
+      <c r="D16" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="E16" s="25"/>
     </row>
     <row r="17" spans="1:5" ht="54" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>14</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="E17" s="32"/>
+      <c r="B17" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" s="27"/>
+      <c r="D17" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="E17" s="27"/>
     </row>
     <row r="18" spans="1:5" ht="144" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>15</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="C18" s="26"/>
+      <c r="B18" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="C18" s="22"/>
       <c r="D18" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4441,67 +4501,67 @@
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="50.44140625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="21.21875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="13" style="9" customWidth="1"/>
-    <col min="6" max="6" width="19" style="9" customWidth="1"/>
-    <col min="7" max="7" width="22" style="9" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" style="9" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" style="9" customWidth="1"/>
-    <col min="10" max="11" width="8.88671875" style="9"/>
-    <col min="12" max="12" width="20.5546875" style="9" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="8.6640625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="50.44140625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="21.21875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="13" style="7" customWidth="1"/>
+    <col min="6" max="6" width="19" style="7" customWidth="1"/>
+    <col min="7" max="7" width="22" style="7" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" style="7" customWidth="1"/>
+    <col min="10" max="11" width="8.88671875" style="7"/>
+    <col min="12" max="12" width="20.5546875" style="7" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H1" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="I1" s="48"/>
+      <c r="H1" s="46" t="s">
+        <v>258</v>
+      </c>
+      <c r="I1" s="47"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H2" s="33" t="s">
-        <v>280</v>
-      </c>
-      <c r="I2" s="28">
+      <c r="H2" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="I2" s="24">
         <f>COUNTIF($E$8:$E$20, "New")</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H3" s="33" t="s">
-        <v>281</v>
-      </c>
-      <c r="I3" s="28">
+      <c r="H3" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="I3" s="24">
         <f>COUNTIF($E$8:$E$20, "In Progress")</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H4" s="33" t="s">
-        <v>282</v>
-      </c>
-      <c r="I4" s="28">
+      <c r="H4" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="I4" s="24">
         <f>COUNTIF($E$8:$E$20, "Pass")</f>
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H5" s="33" t="s">
-        <v>283</v>
-      </c>
-      <c r="I5" s="28">
+      <c r="H5" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="I5" s="24">
         <f>COUNTIF($E$8:$E$20, "Fail")</f>
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H6" s="33" t="s">
-        <v>284</v>
-      </c>
-      <c r="I6" s="28">
+      <c r="H6" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="I6" s="24">
         <f>COUNTIF($E$8:$E$20, "Blocked")</f>
         <v>0</v>
       </c>
@@ -4511,39 +4571,39 @@
         <v>0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B8" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="B8" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>2</v>
@@ -4552,19 +4612,19 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B9" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="B9" s="25" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>13</v>
@@ -4573,42 +4633,42 @@
     </row>
     <row r="10" spans="1:9" ht="36" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B10" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="B10" s="26" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="36" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B11" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="B11" s="25" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>31</v>
@@ -4617,19 +4677,19 @@
     </row>
     <row r="12" spans="1:9" ht="36" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>129</v>
+        <v>261</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>125</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>32</v>
@@ -4638,174 +4698,174 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B13" s="29" t="s">
+        <v>264</v>
+      </c>
+      <c r="B13" s="25" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="36" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>75</v>
+        <v>265</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>74</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:9" ht="54" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B15" s="29" t="s">
-        <v>72</v>
+        <v>266</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>71</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:9" ht="54" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>73</v>
+        <v>267</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>72</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G16" s="3"/>
     </row>
     <row r="17" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B17" s="29" t="s">
-        <v>98</v>
+        <v>268</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>95</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G17" s="3"/>
     </row>
     <row r="18" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>77</v>
+        <v>269</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>76</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G18" s="3"/>
     </row>
     <row r="19" spans="1:7" ht="36" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B19" s="29" t="s">
-        <v>80</v>
+        <v>270</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>79</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:7" ht="90" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="108" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="B20" s="29" t="s">
-        <v>215</v>
+        <v>271</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>208</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -4846,87 +4906,87 @@
   <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="11" customWidth="1"/>
-    <col min="2" max="2" width="25" style="11" customWidth="1"/>
-    <col min="3" max="3" width="27.5546875" style="11" customWidth="1"/>
-    <col min="4" max="4" width="31.21875" style="11" customWidth="1"/>
-    <col min="5" max="5" width="33.6640625" style="11" customWidth="1"/>
-    <col min="6" max="6" width="23.5546875" style="11" customWidth="1"/>
-    <col min="7" max="7" width="22.77734375" style="11" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" style="11" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" style="11" customWidth="1"/>
-    <col min="10" max="10" width="18.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="22.77734375" style="11" customWidth="1"/>
-    <col min="12" max="12" width="50.6640625" style="11" customWidth="1"/>
-    <col min="13" max="13" width="12.33203125" style="11" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="11"/>
+    <col min="1" max="1" width="10.6640625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="25" style="8" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="31.21875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="33.6640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="23.5546875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="22.77734375" style="8" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" style="8" customWidth="1"/>
+    <col min="9" max="9" width="11.109375" style="8" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" style="8" customWidth="1"/>
+    <col min="11" max="11" width="22.77734375" style="8" customWidth="1"/>
+    <col min="12" max="12" width="50.6640625" style="8" customWidth="1"/>
+    <col min="13" max="13" width="13.77734375" style="8" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="34.799999999999997" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="M1" s="37" t="s">
-        <v>314</v>
+        <v>302</v>
+      </c>
+      <c r="M1" s="32" t="s">
+        <v>304</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="162" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="B2" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>312</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E2" s="35" t="s">
-        <v>306</v>
+        <v>296</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>298</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>40</v>
@@ -4935,42 +4995,42 @@
         <v>40</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="M2" s="38" t="s">
-        <v>315</v>
+        <v>345</v>
+      </c>
+      <c r="M2" s="33" t="s">
+        <v>305</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="162" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B3" s="35" t="s">
-        <v>316</v>
+        <v>284</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>306</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>40</v>
@@ -4979,42 +5039,42 @@
         <v>40</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="252" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>327</v>
+        <v>316</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>317</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>39</v>
@@ -5023,42 +5083,42 @@
         <v>39</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="K4" s="35" t="s">
-        <v>332</v>
+        <v>351</v>
+      </c>
+      <c r="K4" s="30" t="s">
+        <v>321</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="M4" s="38" t="s">
-        <v>315</v>
+        <v>323</v>
+      </c>
+      <c r="M4" s="33" t="s">
+        <v>305</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="266.39999999999998" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>39</v>
@@ -5067,63 +5127,63 @@
         <v>39</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="K5" s="35" t="s">
-        <v>342</v>
+        <v>351</v>
+      </c>
+      <c r="K5" s="30" t="s">
+        <v>329</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="162" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>348</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="K6" s="36" t="s">
         <v>351</v>
       </c>
+      <c r="K6" s="31" t="s">
+        <v>335</v>
+      </c>
       <c r="L6" s="2" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -5167,22 +5227,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -5198,27 +5258,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -5232,167 +5292,167 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="9"/>
-    <col min="2" max="2" width="40" style="9" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="40" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
+      <c r="A1" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>104</v>
-      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="22"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="22"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="22"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="22"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="22"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="22"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="22"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="22"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="22"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="22"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="22"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="22"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="22"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5409,181 +5469,181 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="9"/>
-    <col min="2" max="2" width="40" style="9" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="40" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="42" t="s">
+      <c r="E3" s="36" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.35">
+      <c r="A4" s="10">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="12"/>
+    </row>
+    <row r="5" spans="1:5" ht="54" x14ac:dyDescent="0.35">
+      <c r="A5" s="10">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.35">
-      <c r="A4" s="13">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="C5" s="12"/>
+      <c r="D5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" s="12"/>
+    </row>
+    <row r="6" spans="1:5" ht="54" x14ac:dyDescent="0.35">
+      <c r="A6" s="10">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" s="15"/>
-    </row>
-    <row r="5" spans="1:5" ht="54" x14ac:dyDescent="0.35">
-      <c r="A5" s="13">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="15"/>
-    </row>
-    <row r="6" spans="1:5" ht="54" x14ac:dyDescent="0.35">
-      <c r="A6" s="13">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6" s="15"/>
+      <c r="E6" s="12"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="19"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="21"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="18"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="12"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="12"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="12"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="12"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="12"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="12"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="12"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5603,47 +5663,47 @@
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="9"/>
-    <col min="2" max="2" width="40" style="9" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="40" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
+      <c r="A1" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
     </row>
     <row r="2" spans="1:5" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="A2" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>104</v>
+      <c r="D3" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="43.8" x14ac:dyDescent="0.35">
@@ -5651,105 +5711,105 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>113</v>
+        <v>279</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4" s="15"/>
+        <v>115</v>
+      </c>
+      <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="15"/>
+      <c r="B5" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="12"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5769,75 +5829,75 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="9"/>
-    <col min="2" max="2" width="40" style="9" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="40" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
-        <v>121</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
+      <c r="A1" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
     </row>
     <row r="2" spans="1:5" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="A2" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>104</v>
+      <c r="D3" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.35">
-      <c r="A4" s="13">
+      <c r="A4" s="10">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="15"/>
+        <v>118</v>
+      </c>
+      <c r="C4" s="12"/>
       <c r="D4" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E4" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="19"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="21"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="19"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="21"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5854,64 +5914,64 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="9"/>
-    <col min="2" max="2" width="40" style="9" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="40" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
+      <c r="A1" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
     </row>
     <row r="2" spans="1:5" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="44" t="s">
-        <v>124</v>
-      </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="46"/>
+      <c r="A2" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="45"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>104</v>
+      <c r="D3" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="198" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>126</v>
+      <c r="B4" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="C4" s="3">
         <v>-5</v>
       </c>
-      <c r="D4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>132</v>
+      <c r="D4" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="72" x14ac:dyDescent="0.35">
@@ -5919,76 +5979,76 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="14"/>
+        <v>114</v>
+      </c>
+      <c r="C5" s="11"/>
       <c r="D5" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="22"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="22"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6005,64 +6065,64 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="9"/>
-    <col min="2" max="2" width="40" style="9" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="40" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
+      <c r="A1" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
     </row>
     <row r="2" spans="1:5" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="44" t="s">
-        <v>124</v>
-      </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="46"/>
+      <c r="A2" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="45"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>104</v>
+      <c r="D3" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="180" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>130</v>
+      <c r="B4" s="14" t="s">
+        <v>341</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>133</v>
+        <v>123</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="72" x14ac:dyDescent="0.35">
@@ -6070,76 +6130,76 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="14"/>
+        <v>114</v>
+      </c>
+      <c r="C5" s="11"/>
       <c r="D5" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="22"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="22"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6156,195 +6216,195 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="9"/>
-    <col min="2" max="2" width="40" style="9" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="40" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
+      <c r="A1" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
+      <c r="A2" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="23" t="s">
+      <c r="D3" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.35">
+      <c r="A4" s="10">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.35">
-      <c r="A4" s="13">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>107</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" s="15"/>
+        <v>105</v>
+      </c>
+      <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A5" s="13">
+      <c r="A5" s="10">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>198</v>
+        <v>350</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E5" s="15"/>
+        <v>192</v>
+      </c>
+      <c r="E5" s="12"/>
     </row>
     <row r="6" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="E6" s="29"/>
+      <c r="D6" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6" s="25"/>
     </row>
     <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>202</v>
+      <c r="B7" s="25" t="s">
+        <v>195</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="E7" s="29"/>
+      <c r="D7" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="E7" s="25"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="22"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="22"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="22"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="22"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="22"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="22"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="22"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="22"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="22"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6364,241 +6424,241 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="9"/>
-    <col min="2" max="2" width="40" style="9" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="2" width="40" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
-        <v>175</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
+      <c r="A1" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
     </row>
     <row r="2" spans="1:5" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="A2" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>104</v>
+      <c r="D3" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" s="17"/>
+      <c r="B4" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>138</v>
+      <c r="B5" s="14" t="s">
+        <v>133</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" s="17"/>
+      <c r="D5" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:5" ht="54" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>3</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>139</v>
+      <c r="B6" s="14" t="s">
+        <v>134</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="E6" s="17"/>
+      <c r="D6" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>151</v>
+      <c r="B7" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="E7" s="17"/>
+        <v>137</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>5</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>152</v>
+      <c r="B8" s="14" t="s">
+        <v>146</v>
       </c>
       <c r="C8" s="3">
         <v>611945025</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="E8" s="17"/>
+      <c r="D8" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>6</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>140</v>
+      <c r="B9" s="14" t="s">
+        <v>135</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="E9" s="17"/>
+        <v>136</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>7</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>153</v>
+      <c r="B10" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
       </c>
-      <c r="D10" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="E10" s="17"/>
+      <c r="D10" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="1:5" ht="36" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>8</v>
       </c>
-      <c r="B11" s="26" t="s">
-        <v>148</v>
+      <c r="B11" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="17"/>
+      <c r="D11" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5" ht="232.8" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>162</v>
+      <c r="E12" s="23" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="90" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>10</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>163</v>
+      <c r="E13" s="14" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="22"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
